--- a/conversion_table.xlsx
+++ b/conversion_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,12 +374,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ankafobe</t>
+          <t>ivohiboro</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ankafobe</t>
+          <t>Ivohiboro</t>
         </is>
       </c>
       <c r="C2">
@@ -389,12 +389,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ivohiboro</t>
+          <t>tsinjoarivo ambalaomby</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ivohiboro</t>
+          <t>Tsinjoarivo Ambalaomby</t>
         </is>
       </c>
       <c r="C3">
@@ -404,12 +404,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tsinjoarivo ambalaomby</t>
+          <t>ankafobe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tsinjoarivo Ambalaomby</t>
+          <t>Ankafobe</t>
         </is>
       </c>
       <c r="C4">
@@ -434,42 +434,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>oronjia</t>
+          <t>foret naturelle de tsitongambarika</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oronjia</t>
+          <t>Forêt Naturelle de Tsitongambarika</t>
         </is>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foret naturelle de tsitongambarika</t>
+          <t>complexe zones humides mahavavy kinkony</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forêt Naturelle de Tsitongambarika</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C7">
-        <v>0.02941176470588235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>complexe zones humides mahavavy kinkony</t>
+          <t>ambodivahibe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Ambodivahibe</t>
         </is>
       </c>
       <c r="C8">
@@ -479,12 +479,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ambodivahibe</t>
+          <t>maromizaha</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ambodivahibe</t>
+          <t>Maromizaha</t>
         </is>
       </c>
       <c r="C9">
@@ -494,12 +494,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>maromizaha</t>
+          <t>nosy antsoha</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maromizaha</t>
+          <t>Nosy Antsoha</t>
         </is>
       </c>
       <c r="C10">
@@ -509,87 +509,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nosy antsoha</t>
+          <t>ambohitr' antsingy montagne des français</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nosy Antsoha</t>
+          <t>Ambohitr'Antsingy Montagne des Français</t>
         </is>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ambohitr' antsingy montagne des français</t>
+          <t>paysage harmonieux protégée bemanevika</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ambohitr'Antsingy Montagne des Français</t>
+          <t>Complexe des Zones Humides de Bemanevika</t>
         </is>
       </c>
       <c r="C12">
-        <v>0.025</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>paysage harmonieux protégée bemanevika</t>
+          <t>sakara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Complexe des Zones Humides de Bemanevika</t>
+          <t>Makira</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sakara</t>
+          <t>corridor ankeniheny-zahamena</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Makira</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C14">
-        <v>0.3333333333333333</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>behara tranomaro</t>
+          <t>corridor forestier ambositra-vondrozo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Behara-Tranomaro</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.0625</v>
+        <v>0.02702702702702703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sud-ouest ifotaky</t>
+          <t>iles barren</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sud-Ouest Ifotaky</t>
+          <t>Iles Barren</t>
         </is>
       </c>
       <c r="C16">
@@ -599,12 +599,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>torotorofotsy</t>
+          <t>loky manambato</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Torotorofotsy</t>
+          <t>Loky Manambato</t>
         </is>
       </c>
       <c r="C17">
@@ -614,27 +614,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ambohidray</t>
+          <t>complexe mahavavy kinkony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ambohidray</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.358974358974359</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>angavo</t>
+          <t>menabe antimena</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Angavo</t>
+          <t>Menabe Antimena</t>
         </is>
       </c>
       <c r="C19">
@@ -644,57 +644,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ranobe bay</t>
+          <t>corridor marojejy anjanaharibe tsaratanana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ranobe Bay</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vohidefo</t>
+          <t>nouvelle aire protégée manjakatompo-ankaratra</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vohidefo</t>
+          <t>Manjakatompo Ankaratra</t>
         </is>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bombetoka belobaka</t>
+          <t>corridor ankeniheny zahamena</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bombetoka Beloboka</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C22">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ranobe pk 32</t>
+          <t>corridor forestier ambositra vondrozo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ranobe PK 32</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C23">
@@ -704,12 +704,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ambararata londa</t>
+          <t>makira</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ambararata Londa</t>
+          <t>Makira</t>
         </is>
       </c>
       <c r="C24">
@@ -719,42 +719,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nord-ifotaka</t>
+          <t>complexe de zones humides de la mangoky</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nord fotaky</t>
+          <t>Complexe des Zones Humides de Bemanevika</t>
         </is>
       </c>
       <c r="C25">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>amoron'i onilahy</t>
+          <t>complexe manambolomaty</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amoron'i Onilahy</t>
+          <t>Complexe Tsimembo Manambolomaty</t>
         </is>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.2903225806451613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ambatotsirongorongo</t>
+          <t>massif d'ibity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ambatotsirongorongo</t>
+          <t>Massif d'Ibity</t>
         </is>
       </c>
       <c r="C27">
@@ -764,102 +764,102 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ankarabolava</t>
+          <t>forêt de tsitongambarika</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ankarabolava</t>
+          <t>Forêt Naturelle de Tsitongambarika</t>
         </is>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>agnakatrika</t>
+          <t>alan' i vohibe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agnakatrika</t>
+          <t>Ambodivahibe</t>
         </is>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ampanangandehibe-behasina</t>
+          <t>ranobe pk 32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ampanganandehibe-Behasina</t>
+          <t>Ranobe PK 32</t>
         </is>
       </c>
       <c r="C30">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>analalava</t>
+          <t>allée des baobab</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Allées des Baobabs</t>
         </is>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor ankeniheny-zahamena</t>
+          <t>nord-lfotaky</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Nord fotaky</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.03571428571428571</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor forestier ambositra-vondrozo</t>
+          <t>tampolo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C33">
-        <v>0.02702702702702703</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lac alaotra</t>
+          <t>ambatotsirongorongo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lac Alaotra</t>
+          <t>Ambatotsirongorongo</t>
         </is>
       </c>
       <c r="C34">
@@ -869,12 +869,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rivière nosivolo</t>
+          <t>mandena</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rivière Nosivolo</t>
+          <t>Mandena</t>
         </is>
       </c>
       <c r="C35">
@@ -884,37 +884,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>loky manambato</t>
+          <t>kodida</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Loky Manambato</t>
+          <t>Ankodida</t>
         </is>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>menabe antimena</t>
+          <t>ambato atsinanana (sainte luce)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Menabe Antimena</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>0.4838709677419355</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>complexe anjozorobe-angavo</t>
+          <t>couloir forestier d’anjozorobe-angavo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -923,63 +923,63 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.03846153846153846</v>
+        <v>0.4324324324324325</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>massif d'ibity</t>
+          <t>complexe mikea</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Massif d'Ibity</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pointe à larrée</t>
+          <t>complexe mahavavy-kinkony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Réserve spéciale Pointe à Larrée</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C40">
-        <v>0.53125</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vohidava-betsimilaho</t>
+          <t>amoron'i onilahy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vohidava Betsimalao</t>
+          <t>Amoron'i Onilahy</t>
         </is>
       </c>
       <c r="C41">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ambohitr'antsingy montagne des français</t>
+          <t>lac alaotra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ambohitr'Antsingy Montagne des Français</t>
+          <t>Lac Alaotra</t>
         </is>
       </c>
       <c r="C42">
@@ -989,192 +989,192 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tsinjoriake</t>
+          <t>complexe andreba</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tsinjoriake</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mahialambo</t>
+          <t>corridor forestier ankeniheny-zahamena</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mahialambo</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>0.2894736842105263</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>analabe betanatanana</t>
+          <t>corridor forestier bongolava</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Analabe-Betanatanana</t>
+          <t>Corridor forestier Bongolava</t>
         </is>
       </c>
       <c r="C45">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>allée des baobabs</t>
+          <t>montagne des français</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Allées des Baobabs</t>
+          <t>Ambohitr'Antsingy Montagne des Français</t>
         </is>
       </c>
       <c r="C46">
-        <v>0.05555555555555555</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>andrafiamena andavakoera</t>
+          <t>corridor forestier fandriana- vondrozo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Andrafiamena Andavakoera</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>velondriake</t>
+          <t>forêt d'analalava</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Velondriake</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ampasindava</t>
+          <t>ambato-antsinanana (sainte-luce)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ampasindava</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>galoko-kalobinono</t>
+          <t>menabe central</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Galoko Kalobinono</t>
+          <t>Menabe Antimena</t>
         </is>
       </c>
       <c r="C50">
-        <v>0.05882352941176471</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>agnalazaha</t>
+          <t>nord-ifotaky</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agnalazaha</t>
+          <t>Nord fotaky</t>
         </is>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>makirovana tsihomanaomby</t>
+          <t>couloir forestier d'anjozorobe-angavo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Makirovana Tsihomanaomby</t>
+          <t>Complexe Anjozorobe Angavo</t>
         </is>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.4324324324324325</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>forêt sacrée alandraza anavelo</t>
+          <t>andohahela</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Forêt Naturel de Petriky</t>
+          <t>Andohahela</t>
         </is>
       </c>
       <c r="C53">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>forêt naturelle de petriky</t>
+          <t>zahamena</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Forêt Naturel de Petriky</t>
+          <t>Zahamena</t>
         </is>
       </c>
       <c r="C54">
-        <v>0.07692307692307693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ambatoatsinanana</t>
+          <t>nosy mangabe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Nosy Mangabe</t>
         </is>
       </c>
       <c r="C55">
@@ -1184,12 +1184,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ankodida</t>
+          <t>montagne d'ambre</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ankodida</t>
+          <t>Montagne d'Ambre</t>
         </is>
       </c>
       <c r="C56">
@@ -1199,12 +1199,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>mandena</t>
+          <t>ankarafantsika</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mandena</t>
+          <t>Ankarafantsika</t>
         </is>
       </c>
       <c r="C57">
@@ -1214,27 +1214,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>complexe des aires protégées ambohimirahavavy</t>
+          <t>analamazaotra</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Complexe des Zones Humides de Bemanevika</t>
+          <t>Analamazaotra</t>
         </is>
       </c>
       <c r="C58">
-        <v>0.5111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>complexe zones humides mangoky ihotry</t>
+          <t>kirindy mite</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mangoky Ihotry</t>
+          <t>Kirindy Mite</t>
         </is>
       </c>
       <c r="C59">
@@ -1244,12 +1244,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ankarea</t>
+          <t>tsimanampesotse</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ankarea</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C60">
@@ -1259,27 +1259,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mangabe-ranomena-sahasarotra</t>
+          <t>tsingy de bemaraha</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mangabe-Ranomena-Sahasarotra</t>
+          <t>Bemaraha</t>
         </is>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>beanka</t>
+          <t>lokobe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Beanka</t>
+          <t>Lokobe</t>
         </is>
       </c>
       <c r="C62">
@@ -1289,42 +1289,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sahafina</t>
+          <t>tsimanampetsotsa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sahafina</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>marolambo</t>
+          <t>namokora</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marolambo</t>
+          <t>Namoroka</t>
         </is>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>site bioculturel d'antrema</t>
+          <t>mantadia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Site Bioculturel d'Antrema</t>
+          <t>Mantadia</t>
         </is>
       </c>
       <c r="C65">
@@ -1334,12 +1334,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mandrozo</t>
+          <t>marojejy</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mandrozo</t>
+          <t>Marojejy</t>
         </is>
       </c>
       <c r="C66">
@@ -1349,42 +1349,42 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nosy ve androka</t>
+          <t>andrigitra</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nosy Ve Androka</t>
+          <t>Andringitra</t>
         </is>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ankivonjy</t>
+          <t>tsingy-de-bemaraha</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ankivonjy</t>
+          <t>Bemaraha</t>
         </is>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>complexe tsimembo manambolomaty</t>
+          <t>isalo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Complexe Tsimembo Manambolomaty</t>
+          <t>Isalo</t>
         </is>
       </c>
       <c r="C69">
@@ -1394,12 +1394,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>soariake</t>
+          <t>nosy ve androka</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Soariake</t>
+          <t>Nosy Ve Androka</t>
         </is>
       </c>
       <c r="C70">
@@ -1409,357 +1409,357 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ambatofotsy</t>
+          <t>extension apmc kirindy mitea</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ambatofotsy</t>
+          <t>Kirindy Mite</t>
         </is>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ampotaka-ankarabe</t>
+          <t>tsaratanana future sapm</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ampotaka Ankorabe</t>
+          <t>Tsaratanana</t>
         </is>
       </c>
       <c r="C72">
-        <v>0.1176470588235294</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iles barren</t>
+          <t>nosy ve</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Iles Barren</t>
+          <t>Nosy Hara</t>
         </is>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>complexe mahavavy kinkony</t>
+          <t>soatanimbary</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Loky Manambato</t>
         </is>
       </c>
       <c r="C74">
-        <v>0.358974358974359</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>corridor marojejy anjanaharibe tsaratanana</t>
+          <t>andraketa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Andreba</t>
         </is>
       </c>
       <c r="C75">
-        <v>0.5714285714285714</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nouvelle aire protégée manjakatompo-ankaratra</t>
+          <t>ambararata londa</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Manjakatompo Ankaratra</t>
+          <t>Ambararata Londa</t>
         </is>
       </c>
       <c r="C76">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>corridor ankeniheny zahamena</t>
+          <t>antrema</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Andreba</t>
         </is>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>corridor forestier ambositra vondrozo</t>
+          <t>antetezana</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Analamerana</t>
         </is>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>makira</t>
+          <t>complexe forestier kalabenono</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Makira</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>0.4871794871794872</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>complexe de zones humides de la mangoky</t>
+          <t>alan'agnalazaha</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Complexe des Zones Humides de Bemanevika</t>
+          <t>Agnalazaha</t>
         </is>
       </c>
       <c r="C80">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>complexe manambolomaty</t>
+          <t>oronjia (orangea)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Complexe Tsimembo Manambolomaty</t>
+          <t>Oronjia</t>
         </is>
       </c>
       <c r="C81">
-        <v>0.2903225806451613</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>forêt de tsitongambarika</t>
+          <t>petriky</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Forêt Naturelle de Tsitongambarika</t>
+          <t>Bemarivo</t>
         </is>
       </c>
       <c r="C82">
-        <v>0.2941176470588235</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>alan' i vohibe</t>
+          <t>beteny</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ambodivahibe</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C83">
-        <v>0.5</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>allée des baobab</t>
+          <t>vohidefo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Allées des Baobabs</t>
+          <t>Vohidefo</t>
         </is>
       </c>
       <c r="C84">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nord-lfotaky</t>
+          <t>angavo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nord fotaky</t>
+          <t>Angavo</t>
         </is>
       </c>
       <c r="C85">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tampolo</t>
+          <t>beanka</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Beanka</t>
         </is>
       </c>
       <c r="C86">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kodida</t>
+          <t>sahafina</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ankodida</t>
+          <t>Sahafina</t>
         </is>
       </c>
       <c r="C87">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ambato atsinanana (sainte luce)</t>
+          <t>behara-tranomaro</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Behara-Tranomaro</t>
         </is>
       </c>
       <c r="C88">
-        <v>0.4838709677419355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>couloir forestier d’anjozorobe-angavo</t>
+          <t>sud-ouest ifotaky</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Complexe Anjozorobe Angavo</t>
+          <t>Sud-Ouest Ifotaky</t>
         </is>
       </c>
       <c r="C89">
-        <v>0.4324324324324325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>complexe mikea</t>
+          <t>corridor entre parcelles i</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Corridor forestier Bongolava</t>
         </is>
       </c>
       <c r="C90">
-        <v>0.4705882352941176</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>complexe mahavavy-kinkony</t>
+          <t>ii d'andohahela</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Andohahela</t>
         </is>
       </c>
       <c r="C91">
-        <v>0.3846153846153846</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>complexe andreba</t>
+          <t>ambatofotsy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Ambatofotsy</t>
         </is>
       </c>
       <c r="C92">
-        <v>0.4117647058823529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>corridor forestier ankeniheny-zahamena</t>
+          <t>analalava i - ii</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C93">
-        <v>0.2894736842105263</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>corridor forestier bongolava</t>
+          <t>mandrozo</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Corridor forestier Bongolava</t>
+          <t>Mandrozo</t>
         </is>
       </c>
       <c r="C94">
@@ -1769,12 +1769,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>montagne des français</t>
+          <t>site ambondrobe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ambohitr'Antsingy Montagne des Français</t>
+          <t>Zones humides d'Ambondrobe</t>
         </is>
       </c>
       <c r="C95">
@@ -1784,177 +1784,177 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>corridor forestier fandriana- vondrozo</t>
+          <t>nosivolo marolambo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Marolambo</t>
         </is>
       </c>
       <c r="C96">
-        <v>0.2105263157894737</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>forêt d'analalava</t>
+          <t>beasina/ampananganandehibe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Ampotaka Ankorabe</t>
         </is>
       </c>
       <c r="C97">
-        <v>0.4705882352941176</v>
+        <v>0.6538461538461539</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ambato-antsinanana (sainte-luce)</t>
+          <t>mahialambo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Mahialambo</t>
         </is>
       </c>
       <c r="C98">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>menabe central</t>
+          <t>complexe anadabolava</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Menabe Antimena</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C99">
-        <v>0.4666666666666667</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nord-ifotaky</t>
+          <t>tirimena-voaimongotse</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nord fotaky</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C100">
-        <v>0.1666666666666667</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>couloir forestier d'anjozorobe-angavo</t>
+          <t>ambia</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Complexe Anjozorobe Angavo</t>
+          <t>Ambohidray</t>
         </is>
       </c>
       <c r="C101">
-        <v>0.4324324324324325</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>massif d'itremo</t>
+          <t>vohipary</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Massif d'Itremo</t>
+          <t>Vohimana</t>
         </is>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>andohahela</t>
+          <t>beompa</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Andohahela</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>zahamena</t>
+          <t>marobasia</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Zahamena</t>
+          <t>Mantadia</t>
         </is>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nosy mangabe</t>
+          <t>vohimena</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nosy Mangabe</t>
+          <t>Vohimana</t>
         </is>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>montagne d'ambre</t>
+          <t>mangabe</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Montagne d'Ambre</t>
+          <t>Nosy Mangabe</t>
         </is>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ankarafantsika</t>
+          <t>ambohidray</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ankarafantsika</t>
+          <t>Ambohidray</t>
         </is>
       </c>
       <c r="C107">
@@ -1964,252 +1964,252 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>analamazaotra</t>
+          <t>vohibola</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Analamazaotra</t>
+          <t>Ivohiboro</t>
         </is>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kirindy mite</t>
+          <t>complexe forestier makirovana tsihomanaomby</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kirindy Mite</t>
+          <t>Makirovana Tsihomanaomby</t>
         </is>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>0.4418604651162791</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tsimanampesotse</t>
+          <t>pointe larre</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Cap Sainte Marie</t>
         </is>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mikea</t>
+          <t>fort de vohipaho/ankarabolava</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mikea</t>
+          <t>Ankarabolava</t>
         </is>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>0.5862068965517241</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nosy hara</t>
+          <t>fort sacre d'analavelona</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nosy Hara</t>
+          <t>Analavelona</t>
         </is>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>0.5416666666666666</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tsingy de bemaraha</t>
+          <t>bemanevika</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bemaraha</t>
+          <t>Bemanevika</t>
         </is>
       </c>
       <c r="C113">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nosy tanikely</t>
+          <t>takarindaona</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nosy Tanihely</t>
+          <t>Ampasindava</t>
         </is>
       </c>
       <c r="C114">
-        <v>0.07692307692307693</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>lokobe</t>
+          <t>salary bay</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lokobe</t>
+          <t>Ranobe Bay</t>
         </is>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sahamalaza/iles radama</t>
+          <t>extension ala maiky ankodida tsimelahy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sahamalaza Iles Radama</t>
+          <t>Menabe Antimena</t>
         </is>
       </c>
       <c r="C116">
-        <v>0.04545454545454546</v>
+        <v>0.7105263157894737</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>tsimanampetsotsa</t>
+          <t>extension ala maiky ampamalora</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Tsinjoarivo Ambalaomby</t>
         </is>
       </c>
       <c r="C117">
-        <v>0.125</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>namokora</t>
+          <t>site ramsar torotorofotsy</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Namoroka</t>
+          <t>Torotorofotsy</t>
         </is>
       </c>
       <c r="C118">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mantadia</t>
+          <t>amp mitsio tsarabanjina</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mantadia</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>marojejy</t>
+          <t>apmc nosy iranja - ankazoberavina - baie de russe</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marojejy</t>
+          <t>Ampotaka Ankorabe</t>
         </is>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>andrigitra</t>
+          <t>massif d'itremo</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Andringitra</t>
+          <t>Massif d'Itremo</t>
         </is>
       </c>
       <c r="C121">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>befotaka midongy</t>
+          <t>ambohidena</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Befotaka Midongy</t>
+          <t>Ambohidray</t>
         </is>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>zombitse-vohibasia</t>
+          <t>ampanihy</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zombitse Vohibasia</t>
+          <t>Ampasindava</t>
         </is>
       </c>
       <c r="C123">
-        <v>0.05555555555555555</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>baie de baly</t>
+          <t>andrafiamena andavakoera</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Baie de Baly</t>
+          <t>Andrafiamena Andavakoera</t>
         </is>
       </c>
       <c r="C124">
@@ -2219,237 +2219,237 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>tsingy-de-bemaraha</t>
+          <t>bombetoka-belemboka</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bemaraha</t>
+          <t>Bombetoka Beloboka</t>
         </is>
       </c>
       <c r="C125">
-        <v>0.5555555555555556</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>masoala</t>
+          <t>kalalao</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Masoala</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>isalo</t>
+          <t>ankorabe</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Isalo</t>
+          <t>Ankingabe</t>
         </is>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>extension apmc kirindy mitea</t>
+          <t>sahavoa</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kirindy Mite</t>
+          <t>Sahafina</t>
         </is>
       </c>
       <c r="C128">
-        <v>0.5714285714285714</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>tsaratanana future sapm</t>
+          <t>velondriake</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tsaratanana</t>
+          <t>Velondriake</t>
         </is>
       </c>
       <c r="C129">
-        <v>0.5217391304347826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>nosy ve</t>
+          <t>mahasoa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nosy Hara</t>
+          <t>Sahafina</t>
         </is>
       </c>
       <c r="C130">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>soatanimbary</t>
+          <t>summit tsaratanana - ambohimirahavavy -corridor marojejy / a</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Loky Manambato</t>
+          <t>Complexe des  AP Ambohimirahavavy Marivorahona</t>
         </is>
       </c>
       <c r="C131">
-        <v>0.5714285714285714</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>andraketa</t>
+          <t>tsinjoriake</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Andreba</t>
+          <t>Tsinjoriake</t>
         </is>
       </c>
       <c r="C132">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>antrema</t>
+          <t>ekintso</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Andreba</t>
+          <t>Beampingaratsy</t>
         </is>
       </c>
       <c r="C133">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>antetezana</t>
+          <t>extension ala maiky ankodida tranomaro</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Analamerana</t>
+          <t>Behara-Tranomaro</t>
         </is>
       </c>
       <c r="C134">
-        <v>0.4545454545454545</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>complexe forestier kalabenono</t>
+          <t>lokobe extension</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Lokobe</t>
         </is>
       </c>
       <c r="C135">
-        <v>0.4871794871794872</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>alan'agnalazaha</t>
+          <t>fohisokina-ambinanitelo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Agnalazaha</t>
+          <t>Loky Manambato</t>
         </is>
       </c>
       <c r="C136">
-        <v>0.3333333333333333</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>oronjia (orangea)</t>
+          <t>corridor forestier fandriana marolambo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Oronjia</t>
+          <t>Corridor forestier Bongolava</t>
         </is>
       </c>
       <c r="C137">
-        <v>0.5882352941176471</v>
+        <v>0.3947368421052632</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>petriky</t>
+          <t>andringitra</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bemarivo</t>
+          <t>Andringitra</t>
         </is>
       </c>
       <c r="C138">
-        <v>0.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>beteny</t>
+          <t>manongarivo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Manongarivo</t>
         </is>
       </c>
       <c r="C139">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>behara-tranomaro</t>
+          <t>ambatovaky</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Behara-Tranomaro</t>
+          <t>Ambatovaky</t>
         </is>
       </c>
       <c r="C140">
@@ -2459,870 +2459,225 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>corridor entre parcelles i</t>
+          <t>beza-mahafaly</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Corridor forestier Bongolava</t>
+          <t>Beza Mahafaly</t>
         </is>
       </c>
       <c r="C141">
-        <v>0.5714285714285714</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ii d'andohahela</t>
+          <t>cap sainte marie</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Andohahela</t>
+          <t>Cap Sainte Marie</t>
         </is>
       </c>
       <c r="C142">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>analalava i - ii</t>
+          <t>anjanaharibe-sud</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Anjanaharibe_sud</t>
         </is>
       </c>
       <c r="C143">
-        <v>0.4375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>site ambondrobe</t>
+          <t>forêt d'ambohitantely</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Zones humides d'Ambondrobe</t>
+          <t>Ambohitantely</t>
         </is>
       </c>
       <c r="C144">
-        <v>0.4615384615384616</v>
+        <v>0.3809523809523809</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nosivolo marolambo</t>
+          <t>manombo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Marolambo</t>
+          <t>Manombo</t>
         </is>
       </c>
       <c r="C145">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>beasina/ampananganandehibe</t>
+          <t>île de mangabe</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ampotaka Ankorabe</t>
+          <t>Nosy Mangabe</t>
         </is>
       </c>
       <c r="C146">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>complexe anadabolava</t>
+          <t>ambatovavy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Ambatovaky</t>
         </is>
       </c>
       <c r="C147">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tirimena-voaimongotse</t>
+          <t>pic d'ivohibe</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Ambodivahibe</t>
         </is>
       </c>
       <c r="C148">
-        <v>0.5238095238095238</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ambia</t>
+          <t>mangerivola</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ambohidray</t>
+          <t>Mangerivola</t>
         </is>
       </c>
       <c r="C149">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vohipary</t>
+          <t>cap sainte-marie</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vohimana</t>
+          <t>Cap Sainte Marie</t>
         </is>
       </c>
       <c r="C150">
-        <v>0.375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>beompa</t>
+          <t>forêt d'ambre</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Montagne d'Ambre</t>
         </is>
       </c>
       <c r="C151">
-        <v>0.4444444444444444</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>marobasia</t>
+          <t>forêt tampoketsa d'analamaitso</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Mantadia</t>
+          <t>Tampoketsa Analamaitso</t>
         </is>
       </c>
       <c r="C152">
-        <v>0.4444444444444444</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vohimena</t>
+          <t>andranomena</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vohimana</t>
+          <t>Andranomena</t>
         </is>
       </c>
       <c r="C153">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>mangabe</t>
+          <t>ambohijanahary</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nosy Mangabe</t>
+          <t>Ambohijanahary</t>
         </is>
       </c>
       <c r="C154">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>vohibola</t>
+          <t>analamozaotra</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ivohiboro</t>
+          <t>Analamazaotra</t>
         </is>
       </c>
       <c r="C155">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>complexe forestier makirovana tsihomanaomby</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Makirovana Tsihomanaomby</t>
-        </is>
-      </c>
-      <c r="C156">
-        <v>0.4418604651162791</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>pointe larre</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Cap Sainte Marie</t>
-        </is>
-      </c>
-      <c r="C157">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>fort de vohipaho/ankarabolava</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Ankarabolava</t>
-        </is>
-      </c>
-      <c r="C158">
-        <v>0.5862068965517241</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>fort sacre d'analavelona</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Analavelona</t>
-        </is>
-      </c>
-      <c r="C159">
-        <v>0.5416666666666666</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>bemanevika</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Bemanevika</t>
-        </is>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>takarindaona</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Ampasindava</t>
-        </is>
-      </c>
-      <c r="C161">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>salary bay</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Ranobe Bay</t>
-        </is>
-      </c>
-      <c r="C162">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>extension ala maiky ankodida tsimelahy</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Menabe Antimena</t>
-        </is>
-      </c>
-      <c r="C163">
-        <v>0.7105263157894737</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>extension ala maiky ampamalora</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Tsinjoarivo Ambalaomby</t>
-        </is>
-      </c>
-      <c r="C164">
-        <v>0.6333333333333333</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>site ramsar torotorofotsy</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Torotorofotsy</t>
-        </is>
-      </c>
-      <c r="C165">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>amp mitsio tsarabanjina</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Ambatoatsinanana</t>
-        </is>
-      </c>
-      <c r="C166">
-        <v>0.5652173913043478</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>apmc nosy iranja - ankazoberavina - baie de russe</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Ampotaka Ankorabe</t>
-        </is>
-      </c>
-      <c r="C167">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>ambohidena</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Ambohidray</t>
-        </is>
-      </c>
-      <c r="C168">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>ampanihy</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Ampasindava</t>
-        </is>
-      </c>
-      <c r="C169">
-        <v>0.5454545454545454</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>bombetoka-belemboka</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Bombetoka Beloboka</t>
-        </is>
-      </c>
-      <c r="C170">
-        <v>0.1578947368421053</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>kalalao</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Analalava</t>
-        </is>
-      </c>
-      <c r="C171">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>ankorabe</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Ankingabe</t>
-        </is>
-      </c>
-      <c r="C172">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>sahavoa</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Sahafina</t>
-        </is>
-      </c>
-      <c r="C173">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>mahasoa</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Sahafina</t>
-        </is>
-      </c>
-      <c r="C174">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>summit tsaratanana - ambohimirahavavy -corridor marojejy / a</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Complexe des  AP Ambohimirahavavy Marivorahona</t>
-        </is>
-      </c>
-      <c r="C175">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>ekintso</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Beampingaratsy</t>
-        </is>
-      </c>
-      <c r="C176">
-        <v>0.6428571428571429</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>extension ala maiky ankodida tranomaro</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Behara-Tranomaro</t>
-        </is>
-      </c>
-      <c r="C177">
-        <v>0.6842105263157895</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>lokobe extension</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Lokobe</t>
-        </is>
-      </c>
-      <c r="C178">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>fohisokina-ambinanitelo</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Loky Manambato</t>
-        </is>
-      </c>
-      <c r="C179">
-        <v>0.6521739130434783</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>corridor forestier fandriana marolambo</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Corridor forestier Bongolava</t>
-        </is>
-      </c>
-      <c r="C180">
-        <v>0.3947368421052632</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>andringitra</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Andringitra</t>
-        </is>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>manongarivo</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Manongarivo</t>
-        </is>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>ambatovaky</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Ambatovaky</t>
-        </is>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>beza-mahafaly</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Beza Mahafaly</t>
-        </is>
-      </c>
-      <c r="C184">
-        <v>0.07692307692307693</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>cap sainte marie</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Cap Sainte Marie</t>
-        </is>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>anjanaharibe-sud</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Anjanaharibe_sud</t>
-        </is>
-      </c>
-      <c r="C186">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>forêt d'ambohitantely</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Ambohitantely</t>
-        </is>
-      </c>
-      <c r="C187">
-        <v>0.3809523809523809</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>manombo</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Manombo</t>
-        </is>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>île de mangabe</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Nosy Mangabe</t>
-        </is>
-      </c>
-      <c r="C189">
-        <v>0.4285714285714285</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>ambatovavy</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Ambatovaky</t>
-        </is>
-      </c>
-      <c r="C190">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>pic d'ivohibe</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Ambodivahibe</t>
-        </is>
-      </c>
-      <c r="C191">
-        <v>0.4615384615384616</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>mangerivola</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Mangerivola</t>
-        </is>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>cap sainte-marie</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Cap Sainte Marie</t>
-        </is>
-      </c>
-      <c r="C193">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>forêt d'ambre</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Montagne d'Ambre</t>
-        </is>
-      </c>
-      <c r="C194">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>forêt tampoketsa d'analamaitso</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Tampoketsa Analamaitso</t>
-        </is>
-      </c>
-      <c r="C195">
-        <v>0.2666666666666667</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>andranomena</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Andranomena</t>
-        </is>
-      </c>
-      <c r="C196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>ambohijanahary</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Ambohijanahary</t>
-        </is>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>analamozaotra</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Analamazaotra</t>
-        </is>
-      </c>
-      <c r="C198">
         <v>0.07692307692307693</v>
       </c>
     </row>

--- a/conversion_table.xlsx
+++ b/conversion_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,12 +374,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ivohiboro</t>
+          <t>ankafobe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ivohiboro</t>
+          <t>Ankafobe</t>
         </is>
       </c>
       <c r="C2">
@@ -389,12 +389,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tsinjoarivo ambalaomby</t>
+          <t>ivohiboro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tsinjoarivo Ambalaomby</t>
+          <t>Ivohiboro</t>
         </is>
       </c>
       <c r="C3">
@@ -404,12 +404,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ankafobe</t>
+          <t>tsinjoarivo ambalaomby</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ankafobe</t>
+          <t>Tsinjoarivo Ambalaomby</t>
         </is>
       </c>
       <c r="C4">
@@ -434,42 +434,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foret naturelle de tsitongambarika</t>
+          <t>oronjia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Forêt Naturelle de Tsitongambarika</t>
+          <t>Oronjia</t>
         </is>
       </c>
       <c r="C6">
-        <v>0.02941176470588235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>complexe zones humides mahavavy kinkony</t>
+          <t>foret naturelle de tsitongambarika</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Forêt Naturelle de Tsitongambarika</t>
         </is>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ambodivahibe</t>
+          <t>complexe zones humides mahavavy kinkony</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ambodivahibe</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C8">
@@ -479,12 +479,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>maromizaha</t>
+          <t>ambodivahibe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maromizaha</t>
+          <t>Ambodivahibe</t>
         </is>
       </c>
       <c r="C9">
@@ -494,12 +494,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nosy antsoha</t>
+          <t>maromizaha</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nosy Antsoha</t>
+          <t>Maromizaha</t>
         </is>
       </c>
       <c r="C10">
@@ -509,87 +509,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ambohitr' antsingy montagne des français</t>
+          <t>nosy antsoha</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ambohitr'Antsingy Montagne des Français</t>
+          <t>Nosy Antsoha</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>paysage harmonieux protégée bemanevika</t>
+          <t>ambohitr' antsingy montagne des français</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Complexe des Zones Humides de Bemanevika</t>
+          <t>Ambohitr'Antsingy Montagne des Français</t>
         </is>
       </c>
       <c r="C12">
-        <v>0.6</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sakara</t>
+          <t>paysage harmonieux protégée bemanevika</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Makira</t>
+          <t>Complexe des Zones Humides de Bemanevika</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor ankeniheny-zahamena</t>
+          <t>sakara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Makira</t>
         </is>
       </c>
       <c r="C14">
-        <v>0.03571428571428571</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor forestier ambositra-vondrozo</t>
+          <t>behara tranomaro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Behara-Tranomaro</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.02702702702702703</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iles barren</t>
+          <t>sud-ouest ifotaky</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iles Barren</t>
+          <t>Sud-Ouest Ifotaky</t>
         </is>
       </c>
       <c r="C16">
@@ -599,12 +599,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>loky manambato</t>
+          <t>torotorofotsy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loky Manambato</t>
+          <t>Torotorofotsy</t>
         </is>
       </c>
       <c r="C17">
@@ -614,27 +614,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>complexe mahavavy kinkony</t>
+          <t>ambohidray</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Ambohidray</t>
         </is>
       </c>
       <c r="C18">
-        <v>0.358974358974359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>menabe antimena</t>
+          <t>angavo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Menabe Antimena</t>
+          <t>Angavo</t>
         </is>
       </c>
       <c r="C19">
@@ -644,57 +644,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor marojejy anjanaharibe tsaratanana</t>
+          <t>ranobe bay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Ranobe Bay</t>
         </is>
       </c>
       <c r="C20">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nouvelle aire protégée manjakatompo-ankaratra</t>
+          <t>vohidefo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manjakatompo Ankaratra</t>
+          <t>Vohidefo</t>
         </is>
       </c>
       <c r="C21">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor ankeniheny zahamena</t>
+          <t>bombetoka belobaka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Bombetoka Beloboka</t>
         </is>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor forestier ambositra vondrozo</t>
+          <t>ranobe pk 32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Ranobe PK 32</t>
         </is>
       </c>
       <c r="C23">
@@ -704,12 +704,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>makira</t>
+          <t>ambararata londa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Makira</t>
+          <t>Ambararata Londa</t>
         </is>
       </c>
       <c r="C24">
@@ -719,42 +719,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>complexe de zones humides de la mangoky</t>
+          <t>nord-ifotaka</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Complexe des Zones Humides de Bemanevika</t>
+          <t>Nord fotaky</t>
         </is>
       </c>
       <c r="C25">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>complexe manambolomaty</t>
+          <t>amoron'i onilahy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Complexe Tsimembo Manambolomaty</t>
+          <t>Amoron'i Onilahy</t>
         </is>
       </c>
       <c r="C26">
-        <v>0.2903225806451613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>massif d'ibity</t>
+          <t>ambatotsirongorongo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Massif d'Ibity</t>
+          <t>Ambatotsirongorongo</t>
         </is>
       </c>
       <c r="C27">
@@ -764,102 +764,102 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>forêt de tsitongambarika</t>
+          <t>ankarabolava</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Forêt Naturelle de Tsitongambarika</t>
+          <t>Ankarabolava</t>
         </is>
       </c>
       <c r="C28">
-        <v>0.2941176470588235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>alan' i vohibe</t>
+          <t>agnakatrika</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ambodivahibe</t>
+          <t>Agnakatrika</t>
         </is>
       </c>
       <c r="C29">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ranobe pk 32</t>
+          <t>ampanangandehibe-behasina</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ranobe PK 32</t>
+          <t>Ampanganandehibe-Behasina</t>
         </is>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>allée des baobab</t>
+          <t>analalava</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Allées des Baobabs</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C31">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nord-lfotaky</t>
+          <t>corridor ankeniheny-zahamena</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nord fotaky</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.1666666666666667</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tampolo</t>
+          <t>corridor forestier ambositra-vondrozo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C33">
-        <v>0.4444444444444444</v>
+        <v>0.02702702702702703</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ambatotsirongorongo</t>
+          <t>lac alaotra</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ambatotsirongorongo</t>
+          <t>Lac Alaotra</t>
         </is>
       </c>
       <c r="C34">
@@ -869,12 +869,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mandena</t>
+          <t>rivière nosivolo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mandena</t>
+          <t>Rivière Nosivolo</t>
         </is>
       </c>
       <c r="C35">
@@ -884,37 +884,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kodida</t>
+          <t>loky manambato</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ankodida</t>
+          <t>Loky Manambato</t>
         </is>
       </c>
       <c r="C36">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ambato atsinanana (sainte luce)</t>
+          <t>menabe antimena</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Menabe Antimena</t>
         </is>
       </c>
       <c r="C37">
-        <v>0.4838709677419355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>couloir forestier d’anjozorobe-angavo</t>
+          <t>complexe anjozorobe-angavo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -923,63 +923,63 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.4324324324324325</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>complexe mikea</t>
+          <t>massif d'ibity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Massif d'Ibity</t>
         </is>
       </c>
       <c r="C39">
-        <v>0.4705882352941176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>complexe mahavavy-kinkony</t>
+          <t>pointe à larrée</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Réserve spéciale Pointe à Larrée</t>
         </is>
       </c>
       <c r="C40">
-        <v>0.3846153846153846</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>amoron'i onilahy</t>
+          <t>vohidava-betsimilaho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amoron'i Onilahy</t>
+          <t>Vohidava Betsimalao</t>
         </is>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lac alaotra</t>
+          <t>ambohitr'antsingy montagne des français</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Alaotra</t>
+          <t>Ambohitr'Antsingy Montagne des Français</t>
         </is>
       </c>
       <c r="C42">
@@ -989,192 +989,192 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>complexe andreba</t>
+          <t>tsinjoriake</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Tsinjoriake</t>
         </is>
       </c>
       <c r="C43">
-        <v>0.4117647058823529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor forestier ankeniheny-zahamena</t>
+          <t>mahialambo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Corridor Ankeniheny Zahamena</t>
+          <t>Mahialambo</t>
         </is>
       </c>
       <c r="C44">
-        <v>0.2894736842105263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor forestier bongolava</t>
+          <t>analabe betanatanana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Corridor forestier Bongolava</t>
+          <t>Analabe-Betanatanana</t>
         </is>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>montagne des français</t>
+          <t>allée des baobabs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ambohitr'Antsingy Montagne des Français</t>
+          <t>Allées des Baobabs</t>
         </is>
       </c>
       <c r="C46">
-        <v>0.4615384615384616</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor forestier fandriana- vondrozo</t>
+          <t>andrafiamena andavakoera</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Corridor Forestier Ambositra Vondrozo</t>
+          <t>Andrafiamena Andavakoera</t>
         </is>
       </c>
       <c r="C47">
-        <v>0.2105263157894737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>forêt d'analalava</t>
+          <t>velondriake</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Velondriake</t>
         </is>
       </c>
       <c r="C48">
-        <v>0.4705882352941176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ambato-antsinanana (sainte-luce)</t>
+          <t>ampasindava</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Ampasindava</t>
         </is>
       </c>
       <c r="C49">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>menabe central</t>
+          <t>galoko-kalobinono</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Menabe Antimena</t>
+          <t>Galoko Kalobinono</t>
         </is>
       </c>
       <c r="C50">
-        <v>0.4666666666666667</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nord-ifotaky</t>
+          <t>agnalazaha</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nord fotaky</t>
+          <t>Agnalazaha</t>
         </is>
       </c>
       <c r="C51">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>couloir forestier d'anjozorobe-angavo</t>
+          <t>makirovana tsihomanaomby</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Complexe Anjozorobe Angavo</t>
+          <t>Makirovana Tsihomanaomby</t>
         </is>
       </c>
       <c r="C52">
-        <v>0.4324324324324325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>andohahela</t>
+          <t>forêt sacrée alandraza anavelo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Andohahela</t>
+          <t>Forêt Naturel de Petriky</t>
         </is>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>zahamena</t>
+          <t>forêt naturelle de petriky</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zahamena</t>
+          <t>Forêt Naturel de Petriky</t>
         </is>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nosy mangabe</t>
+          <t>ambatoatsinanana</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nosy Mangabe</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C55">
@@ -1184,12 +1184,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>montagne d'ambre</t>
+          <t>ankodida</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Montagne d'Ambre</t>
+          <t>Ankodida</t>
         </is>
       </c>
       <c r="C56">
@@ -1199,12 +1199,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ankarafantsika</t>
+          <t>mandena</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ankarafantsika</t>
+          <t>Mandena</t>
         </is>
       </c>
       <c r="C57">
@@ -1214,27 +1214,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>analamazaotra</t>
+          <t>complexe des aires protégées ambohimirahavavy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Analamazaotra</t>
+          <t>Complexe des Zones Humides de Bemanevika</t>
         </is>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>0.5111111111111111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kirindy mite</t>
+          <t>complexe zones humides mangoky ihotry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kirindy Mite</t>
+          <t>Complexe Zones Humides Mangoky Ihotry</t>
         </is>
       </c>
       <c r="C59">
@@ -1244,12 +1244,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tsimanampesotse</t>
+          <t>ankarea</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Ankarea</t>
         </is>
       </c>
       <c r="C60">
@@ -1259,27 +1259,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tsingy de bemaraha</t>
+          <t>mangabe-ranomena-sahasarotra</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bemaraha</t>
+          <t>Mangabe-Ranomena-Sahasarotra</t>
         </is>
       </c>
       <c r="C61">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lokobe</t>
+          <t>beanka</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lokobe</t>
+          <t>Beanka</t>
         </is>
       </c>
       <c r="C62">
@@ -1289,42 +1289,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tsimanampetsotsa</t>
+          <t>sahafina</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Sahafina</t>
         </is>
       </c>
       <c r="C63">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>namokora</t>
+          <t>marolambo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Namoroka</t>
+          <t>Marolambo</t>
         </is>
       </c>
       <c r="C64">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mantadia</t>
+          <t>site bioculturel d'antrema</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mantadia</t>
+          <t>Site Bioculturel d'Antrema</t>
         </is>
       </c>
       <c r="C65">
@@ -1334,12 +1334,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>marojejy</t>
+          <t>mandrozo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marojejy</t>
+          <t>Mandrozo</t>
         </is>
       </c>
       <c r="C66">
@@ -1349,42 +1349,42 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>andrigitra</t>
+          <t>nosy ve androka</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Andringitra</t>
+          <t>Nosy Ve Androka</t>
         </is>
       </c>
       <c r="C67">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tsingy-de-bemaraha</t>
+          <t>ankivonjy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bemaraha</t>
+          <t>Ankivonjy</t>
         </is>
       </c>
       <c r="C68">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>isalo</t>
+          <t>complexe tsimembo manambolomaty</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Isalo</t>
+          <t>Complexe Tsimembo Manambolomaty</t>
         </is>
       </c>
       <c r="C69">
@@ -1394,12 +1394,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>nosy ve androka</t>
+          <t>soariake</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nosy Ve Androka</t>
+          <t>Soariake</t>
         </is>
       </c>
       <c r="C70">
@@ -1409,357 +1409,357 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>extension apmc kirindy mitea</t>
+          <t>ambatofotsy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kirindy Mite</t>
+          <t>Ambatofotsy</t>
         </is>
       </c>
       <c r="C71">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tsaratanana future sapm</t>
+          <t>ampotaka-ankarabe</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tsaratanana</t>
+          <t>Ampotaka Ankorabe</t>
         </is>
       </c>
       <c r="C72">
-        <v>0.5217391304347826</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nosy ve</t>
+          <t>iles barren</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nosy Hara</t>
+          <t>Iles Barren</t>
         </is>
       </c>
       <c r="C73">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>soatanimbary</t>
+          <t>complexe mahavavy kinkony</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Loky Manambato</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C74">
-        <v>0.5714285714285714</v>
+        <v>0.358974358974359</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>andraketa</t>
+          <t>corridor marojejy anjanaharibe tsaratanana</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Andreba</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C75">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ambararata londa</t>
+          <t>nouvelle aire protégée manjakatompo-ankaratra</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ambararata Londa</t>
+          <t>Manjakatompo Ankaratra</t>
         </is>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>antrema</t>
+          <t>corridor ankeniheny zahamena</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Andreba</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C77">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>antetezana</t>
+          <t>corridor forestier ambositra vondrozo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Analamerana</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C78">
-        <v>0.4545454545454545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>complexe forestier kalabenono</t>
+          <t>makira</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Complexe Zones Humides Mahavavy Kinkony</t>
+          <t>Makira</t>
         </is>
       </c>
       <c r="C79">
-        <v>0.4871794871794872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>alan'agnalazaha</t>
+          <t>complexe de zones humides de la mangoky</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agnalazaha</t>
+          <t>Complexe des Zones Humides de Bemanevika</t>
         </is>
       </c>
       <c r="C80">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>oronjia (orangea)</t>
+          <t>complexe manambolomaty</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Oronjia</t>
+          <t>Complexe Tsimembo Manambolomaty</t>
         </is>
       </c>
       <c r="C81">
-        <v>0.5882352941176471</v>
+        <v>0.2903225806451613</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>petriky</t>
+          <t>forêt de tsitongambarika</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bemarivo</t>
+          <t>Forêt Naturelle de Tsitongambarika</t>
         </is>
       </c>
       <c r="C82">
-        <v>0.625</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>beteny</t>
+          <t>alan' i vohibe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Ambodivahibe</t>
         </is>
       </c>
       <c r="C83">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>vohidefo</t>
+          <t>allée des baobab</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vohidefo</t>
+          <t>Allées des Baobabs</t>
         </is>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>angavo</t>
+          <t>nord-lfotaky</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Angavo</t>
+          <t>Nord fotaky</t>
         </is>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>beanka</t>
+          <t>tampolo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Beanka</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>sahafina</t>
+          <t>kodida</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sahafina</t>
+          <t>Ankodida</t>
         </is>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>behara-tranomaro</t>
+          <t>ambato atsinanana (sainte luce)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Behara-Tranomaro</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>0.4838709677419355</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sud-ouest ifotaky</t>
+          <t>couloir forestier d’anjozorobe-angavo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sud-Ouest Ifotaky</t>
+          <t>Complexe Anjozorobe Angavo</t>
         </is>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>0.4324324324324325</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>corridor entre parcelles i</t>
+          <t>complexe mikea</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corridor forestier Bongolava</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C90">
-        <v>0.5714285714285714</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ii d'andohahela</t>
+          <t>complexe mahavavy-kinkony</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Andohahela</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C91">
-        <v>0.3333333333333333</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ambatofotsy</t>
+          <t>complexe andreba</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ambatofotsy</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>analalava i - ii</t>
+          <t>corridor forestier ankeniheny-zahamena</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Corridor Ankeniheny Zahamena</t>
         </is>
       </c>
       <c r="C93">
-        <v>0.4375</v>
+        <v>0.2894736842105263</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mandrozo</t>
+          <t>corridor forestier bongolava</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mandrozo</t>
+          <t>Corridor forestier Bongolava</t>
         </is>
       </c>
       <c r="C94">
@@ -1769,12 +1769,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>site ambondrobe</t>
+          <t>montagne des français</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zones humides d'Ambondrobe</t>
+          <t>Ambohitr'Antsingy Montagne des Français</t>
         </is>
       </c>
       <c r="C95">
@@ -1784,177 +1784,177 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nosivolo marolambo</t>
+          <t>corridor forestier fandriana- vondrozo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Marolambo</t>
+          <t>Corridor Forestier Ambositra Vondrozo</t>
         </is>
       </c>
       <c r="C96">
-        <v>0.5</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>beasina/ampananganandehibe</t>
+          <t>forêt d'analalava</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ampotaka Ankorabe</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C97">
-        <v>0.6538461538461539</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mahialambo</t>
+          <t>ambato-antsinanana (sainte-luce)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mahialambo</t>
+          <t>Ambatoatsinanana</t>
         </is>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>complexe anadabolava</t>
+          <t>menabe central</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Complexe Bobaomby</t>
+          <t>Menabe Antimena</t>
         </is>
       </c>
       <c r="C99">
-        <v>0.45</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tirimena-voaimongotse</t>
+          <t>nord-ifotaky</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tsimanampesotse</t>
+          <t>Nord fotaky</t>
         </is>
       </c>
       <c r="C100">
-        <v>0.5238095238095238</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ambia</t>
+          <t>couloir forestier d'anjozorobe-angavo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ambohidray</t>
+          <t>Complexe Anjozorobe Angavo</t>
         </is>
       </c>
       <c r="C101">
-        <v>0.5</v>
+        <v>0.4324324324324325</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>vohipary</t>
+          <t>massif d'itremo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vohimana</t>
+          <t>Massif d'Itremo</t>
         </is>
       </c>
       <c r="C102">
-        <v>0.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>beompa</t>
+          <t>andohahela</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Betampona</t>
+          <t>Andohahela</t>
         </is>
       </c>
       <c r="C103">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>marobasia</t>
+          <t>zahamena</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mantadia</t>
+          <t>Zahamena</t>
         </is>
       </c>
       <c r="C104">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>vohimena</t>
+          <t>nosy mangabe</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vohimana</t>
+          <t>Nosy Mangabe</t>
         </is>
       </c>
       <c r="C105">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mangabe</t>
+          <t>montagne d'ambre</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nosy Mangabe</t>
+          <t>Montagne d'Ambre</t>
         </is>
       </c>
       <c r="C106">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ambohidray</t>
+          <t>ankarafantsika</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ambohidray</t>
+          <t>Ankarafantsika</t>
         </is>
       </c>
       <c r="C107">
@@ -1964,252 +1964,252 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>vohibola</t>
+          <t>analamazaotra</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ivohiboro</t>
+          <t>Analamazaotra</t>
         </is>
       </c>
       <c r="C108">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>complexe forestier makirovana tsihomanaomby</t>
+          <t>kirindy mite</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Makirovana Tsihomanaomby</t>
+          <t>Kirindy Mite</t>
         </is>
       </c>
       <c r="C109">
-        <v>0.4418604651162791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>pointe larre</t>
+          <t>tsimanampesotse</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cap Sainte Marie</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C110">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>fort de vohipaho/ankarabolava</t>
+          <t>mikea</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ankarabolava</t>
+          <t>Mikea</t>
         </is>
       </c>
       <c r="C111">
-        <v>0.5862068965517241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>fort sacre d'analavelona</t>
+          <t>nosy hara</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Analavelona</t>
+          <t>Nosy Hara</t>
         </is>
       </c>
       <c r="C112">
-        <v>0.5416666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bemanevika</t>
+          <t>tsingy de bemaraha</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bemanevika</t>
+          <t>Bemaraha</t>
         </is>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>takarindaona</t>
+          <t>nosy tanikely</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ampasindava</t>
+          <t>Nosy Tanihely</t>
         </is>
       </c>
       <c r="C114">
-        <v>0.5</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>salary bay</t>
+          <t>lokobe</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ranobe Bay</t>
+          <t>Lokobe</t>
         </is>
       </c>
       <c r="C115">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>extension ala maiky ankodida tsimelahy</t>
+          <t>sahamalaza/iles radama</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Menabe Antimena</t>
+          <t>Sahamalaza Iles Radama</t>
         </is>
       </c>
       <c r="C116">
-        <v>0.7105263157894737</v>
+        <v>0.04545454545454546</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>extension ala maiky ampamalora</t>
+          <t>tsimanampetsotsa</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tsinjoarivo Ambalaomby</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C117">
-        <v>0.6333333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>site ramsar torotorofotsy</t>
+          <t>namokora</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Torotorofotsy</t>
+          <t>Namoroka</t>
         </is>
       </c>
       <c r="C118">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>amp mitsio tsarabanjina</t>
+          <t>mantadia</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ambatoatsinanana</t>
+          <t>Mantadia</t>
         </is>
       </c>
       <c r="C119">
-        <v>0.5652173913043478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>apmc nosy iranja - ankazoberavina - baie de russe</t>
+          <t>marojejy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ampotaka Ankorabe</t>
+          <t>Marojejy</t>
         </is>
       </c>
       <c r="C120">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>massif d'itremo</t>
+          <t>andrigitra</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Massif d'Itremo</t>
+          <t>Andringitra</t>
         </is>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ambohidena</t>
+          <t>befotaka midongy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ambohidray</t>
+          <t>Befotaka Midongy</t>
         </is>
       </c>
       <c r="C122">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ampanihy</t>
+          <t>zombitse-vohibasia</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ampasindava</t>
+          <t>Zombitse Vohibasia</t>
         </is>
       </c>
       <c r="C123">
-        <v>0.5454545454545454</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>andrafiamena andavakoera</t>
+          <t>baie de baly</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Andrafiamena Andavakoera</t>
+          <t>Baie de Baly</t>
         </is>
       </c>
       <c r="C124">
@@ -2219,237 +2219,237 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>bombetoka-belemboka</t>
+          <t>tsingy-de-bemaraha</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bombetoka Beloboka</t>
+          <t>Bemaraha</t>
         </is>
       </c>
       <c r="C125">
-        <v>0.1578947368421053</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kalalao</t>
+          <t>masoala</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Analalava</t>
+          <t>Masoala</t>
         </is>
       </c>
       <c r="C126">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ankorabe</t>
+          <t>isalo</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ankingabe</t>
+          <t>Isalo</t>
         </is>
       </c>
       <c r="C127">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sahavoa</t>
+          <t>extension apmc kirindy mitea</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sahafina</t>
+          <t>Kirindy Mite</t>
         </is>
       </c>
       <c r="C128">
-        <v>0.375</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>velondriake</t>
+          <t>tsaratanana future sapm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Velondriake</t>
+          <t>Tsaratanana</t>
         </is>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mahasoa</t>
+          <t>nosy ve</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sahafina</t>
+          <t>Nosy Hara</t>
         </is>
       </c>
       <c r="C130">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>summit tsaratanana - ambohimirahavavy -corridor marojejy / a</t>
+          <t>soatanimbary</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Complexe des  AP Ambohimirahavavy Marivorahona</t>
+          <t>Loky Manambato</t>
         </is>
       </c>
       <c r="C131">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tsinjoriake</t>
+          <t>andraketa</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tsinjoriake</t>
+          <t>Andreba</t>
         </is>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ekintso</t>
+          <t>antrema</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Beampingaratsy</t>
+          <t>Andreba</t>
         </is>
       </c>
       <c r="C133">
-        <v>0.6428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>extension ala maiky ankodida tranomaro</t>
+          <t>antetezana</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Behara-Tranomaro</t>
+          <t>Analamerana</t>
         </is>
       </c>
       <c r="C134">
-        <v>0.6842105263157895</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>lokobe extension</t>
+          <t>complexe forestier kalabenono</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lokobe</t>
+          <t>Complexe Zones Humides Mahavavy Kinkony</t>
         </is>
       </c>
       <c r="C135">
-        <v>0.625</v>
+        <v>0.4871794871794872</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>fohisokina-ambinanitelo</t>
+          <t>alan'agnalazaha</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Loky Manambato</t>
+          <t>Agnalazaha</t>
         </is>
       </c>
       <c r="C136">
-        <v>0.6521739130434783</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>corridor forestier fandriana marolambo</t>
+          <t>oronjia (orangea)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Corridor forestier Bongolava</t>
+          <t>Oronjia</t>
         </is>
       </c>
       <c r="C137">
-        <v>0.3947368421052632</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>andringitra</t>
+          <t>petriky</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Andringitra</t>
+          <t>Bemarivo</t>
         </is>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>manongarivo</t>
+          <t>beteny</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Manongarivo</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ambatovaky</t>
+          <t>behara-tranomaro</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ambatovaky</t>
+          <t>Behara-Tranomaro</t>
         </is>
       </c>
       <c r="C140">
@@ -2459,225 +2459,870 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>beza-mahafaly</t>
+          <t>corridor entre parcelles i</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Beza Mahafaly</t>
+          <t>Corridor forestier Bongolava</t>
         </is>
       </c>
       <c r="C141">
-        <v>0.07692307692307693</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>cap sainte marie</t>
+          <t>ii d'andohahela</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cap Sainte Marie</t>
+          <t>Andohahela</t>
         </is>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>anjanaharibe-sud</t>
+          <t>analalava i - ii</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Anjanaharibe_sud</t>
+          <t>Analalava</t>
         </is>
       </c>
       <c r="C143">
-        <v>0.0625</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>forêt d'ambohitantely</t>
+          <t>site ambondrobe</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ambohitantely</t>
+          <t>Zones humides d'Ambondrobe</t>
         </is>
       </c>
       <c r="C144">
-        <v>0.3809523809523809</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>manombo</t>
+          <t>nosivolo marolambo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Manombo</t>
+          <t>Marolambo</t>
         </is>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>île de mangabe</t>
+          <t>beasina/ampananganandehibe</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nosy Mangabe</t>
+          <t>Ampotaka Ankorabe</t>
         </is>
       </c>
       <c r="C146">
-        <v>0.4285714285714285</v>
+        <v>0.6538461538461539</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ambatovavy</t>
+          <t>complexe anadabolava</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ambatovaky</t>
+          <t>Complexe Bobaomby</t>
         </is>
       </c>
       <c r="C147">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pic d'ivohibe</t>
+          <t>tirimena-voaimongotse</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ambodivahibe</t>
+          <t>Tsimanampesotse</t>
         </is>
       </c>
       <c r="C148">
-        <v>0.4615384615384616</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>mangerivola</t>
+          <t>ambia</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mangerivola</t>
+          <t>Ambohidray</t>
         </is>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>cap sainte-marie</t>
+          <t>vohipary</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cap Sainte Marie</t>
+          <t>Vohimana</t>
         </is>
       </c>
       <c r="C150">
-        <v>0.0625</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>forêt d'ambre</t>
+          <t>beompa</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Montagne d'Ambre</t>
+          <t>Betampona</t>
         </is>
       </c>
       <c r="C151">
-        <v>0.4375</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>forêt tampoketsa d'analamaitso</t>
+          <t>marobasia</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tampoketsa Analamaitso</t>
+          <t>Mantadia</t>
         </is>
       </c>
       <c r="C152">
-        <v>0.2666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>andranomena</t>
+          <t>vohimena</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Andranomena</t>
+          <t>Vohimana</t>
         </is>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ambohijanahary</t>
+          <t>mangabe</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ambohijanahary</t>
+          <t>Nosy Mangabe</t>
         </is>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>vohibola</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ivohiboro</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>complexe forestier makirovana tsihomanaomby</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Makirovana Tsihomanaomby</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.4418604651162791</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>pointe larre</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Cap Sainte Marie</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fort de vohipaho/ankarabolava</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ankarabolava</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.5862068965517241</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>fort sacre d'analavelona</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Analavelona</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0.5416666666666666</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>bemanevika</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Bemanevika</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>takarindaona</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ampasindava</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>salary bay</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ranobe Bay</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>extension ala maiky ankodida tsimelahy</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Menabe Antimena</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0.7105263157894737</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>extension ala maiky ampamalora</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Tsinjoarivo Ambalaomby</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0.6333333333333333</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>site ramsar torotorofotsy</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Torotorofotsy</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>amp mitsio tsarabanjina</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ambatoatsinanana</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.5652173913043478</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>apmc nosy iranja - ankazoberavina - baie de russe</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ampotaka Ankorabe</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ambohidena</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ambohidray</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ampanihy</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ampasindava</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.5454545454545454</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>bombetoka-belemboka</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Bombetoka Beloboka</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.1578947368421053</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>kalalao</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Analalava</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0.4444444444444444</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ankorabe</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ankingabe</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>sahavoa</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sahafina</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>mahasoa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Sahafina</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>summit tsaratanana - ambohimirahavavy -corridor marojejy / a</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Complexe des  AP Ambohimirahavavy Marivorahona</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ekintso</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Beampingaratsy</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>extension ala maiky ankodida tranomaro</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Behara-Tranomaro</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>0.6842105263157895</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>lokobe extension</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Lokobe</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>fohisokina-ambinanitelo</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Loky Manambato</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>0.6521739130434783</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>corridor forestier fandriana marolambo</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Corridor forestier Bongolava</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>0.3947368421052632</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>andringitra</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Andringitra</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>manongarivo</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Manongarivo</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ambatovaky</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ambatovaky</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>beza-mahafaly</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Beza Mahafaly</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>0.07692307692307693</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>cap sainte marie</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Cap Sainte Marie</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>anjanaharibe-sud</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Anjanaharibe_sud</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>forêt d'ambohitantely</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ambohitantely</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>0.3809523809523809</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>manombo</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Manombo</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>île de mangabe</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nosy Mangabe</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>0.4285714285714285</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ambatovavy</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ambatovaky</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>pic d'ivohibe</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ambodivahibe</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>0.4615384615384616</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>mangerivola</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Mangerivola</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>cap sainte-marie</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cap Sainte Marie</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>forêt d'ambre</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Montagne d'Ambre</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>forêt tampoketsa d'analamaitso</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Tampoketsa Analamaitso</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0.2666666666666667</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>andranomena</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Andranomena</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ambohijanahary</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Ambohijanahary</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
           <t>analamozaotra</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Analamazaotra</t>
         </is>
       </c>
-      <c r="C155">
+      <c r="C198">
         <v>0.07692307692307693</v>
       </c>
     </row>
